--- a/results/02_taxa_assemblage/WardsClustering/tables/anova_taxa.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/anova_taxa.xlsx
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>290.5</v>
+        <v>283.17</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>37.84</v>
+        <v>45.18</v>
       </c>
       <c r="F2" t="n">
         <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>180.39</v>
+        <v>147.28</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.85 ± 0.30</t>
+          <t>0.23 ± 0.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.01 ± 0.14</t>
+          <t>6.28 ± 0.11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.23 ± 0.11</t>
+          <t>3.46 ± 0.64</t>
         </is>
       </c>
     </row>
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>135.82</v>
+        <v>109.03</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>79.78</v>
+        <v>106.57</v>
       </c>
       <c r="F3" t="n">
         <v>47</v>
       </c>
       <c r="G3" t="n">
-        <v>40.01</v>
+        <v>24.04</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -556,17 +556,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.11 ± 0.36</t>
+          <t>5.02 ± 0.28</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.68 ± 0.47</t>
+          <t>1.07 ± 0.39</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5.92 ± 0.07</t>
+          <t>4.10 ± 0.50</t>
         </is>
       </c>
     </row>
@@ -580,38 +580,38 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>54</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>108.99</v>
+        <v>91.56</v>
       </c>
       <c r="F4" t="n">
         <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>11.64</v>
+        <v>18.34</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0001***</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.26 ± 0.28</t>
+          <t>4.80 ± 0.27</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.61 ± 0.56</t>
+          <t>1.65 ± 0.55</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4.22 ± 0.33</t>
+          <t>4.62 ± 0.17</t>
         </is>
       </c>
     </row>
@@ -625,38 +625,38 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14.32</v>
+        <v>56.89</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>124.68</v>
+        <v>82.11</v>
       </c>
       <c r="F5" t="n">
         <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7</v>
+        <v>16.28</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0777.</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.07 ± 0.38</t>
+          <t>0.31 ± 0.12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.96 ± 0.59</t>
+          <t>2.84 ± 0.67</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.59 ± 0.26</t>
+          <t>2.13 ± 0.64</t>
         </is>
       </c>
     </row>
@@ -666,42 +666,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.63</v>
+        <v>43.58</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>53.17</v>
+        <v>113.3</v>
       </c>
       <c r="F6" t="n">
         <v>47</v>
       </c>
       <c r="G6" t="n">
-        <v>2.49</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0940.</t>
+          <t>0.0005***</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.29 ± 0.17</t>
+          <t>2.04 ± 0.33</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.08 ± 0.08</t>
+          <t>0.39 ± 0.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.89 ± 0.37</t>
+          <t>3.42 ± 0.30</t>
         </is>
       </c>
     </row>
@@ -711,42 +711,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Turbellaria</t>
+          <t>Hexagenia</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.15</v>
+        <v>11.48</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>20.37</v>
+        <v>40.22</v>
       </c>
       <c r="F7" t="n">
         <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>2.49</v>
+        <v>6.71</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0942.</t>
+          <t>0.0027**</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.21 ± 0.10</t>
+          <t>0.27 ± 0.13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.64 ± 0.31</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.13 ± 0.08</t>
+          <t>1.38 ± 0.51</t>
         </is>
       </c>
     </row>
@@ -756,42 +756,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Acari</t>
+          <t>Turbellaria</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.72</v>
+        <v>4.08</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>30.18</v>
+        <v>18.44</v>
       </c>
       <c r="F8" t="n">
         <v>47</v>
       </c>
       <c r="G8" t="n">
-        <v>2.12</v>
+        <v>5.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.1316</t>
+          <t>0.0091**</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.74 ± 0.25</t>
+          <t>0.11 ± 0.06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.15 ± 0.08</t>
+          <t>0.30 ± 0.30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.57 ± 0.16</t>
+          <t>0.85 ± 0.32</t>
         </is>
       </c>
     </row>
@@ -801,42 +801,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Hirudinea</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12.55</v>
+        <v>0.47</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>144.33</v>
+        <v>4.62</v>
       </c>
       <c r="F9" t="n">
         <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.1410</t>
+          <t>0.1020</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.51 ± 0.47</t>
+          <t>0.05 ± 0.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.24 ± 0.41</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2.07 ± 0.37</t>
+          <t>0.28 ± 0.20</t>
         </is>
       </c>
     </row>
@@ -846,42 +846,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other Trichoptera</t>
+          <t>Acari</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.64</v>
+        <v>2.77</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>8.58</v>
+        <v>30.13</v>
       </c>
       <c r="F10" t="n">
         <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.1853</t>
+          <t>0.1269</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.28 ± 0.12</t>
+          <t>0.57 ± 0.16</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.06 ± 0.06</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.11 ± 0.11</t>
+          <t>0.80 ± 0.28</t>
         </is>
       </c>
     </row>
@@ -891,42 +891,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sphaeriidae</t>
+          <t>Other Trichoptera</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.25</v>
+        <v>0.7</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>8.52</v>
       </c>
       <c r="F11" t="n">
         <v>47</v>
       </c>
       <c r="G11" t="n">
-        <v>1.06</v>
+        <v>1.94</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.3554</t>
+          <t>0.1556</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.82 ± 0.32</t>
+          <t>0.12 ± 0.06</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.45 ± 0.26</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.34 ± 0.13</t>
+          <t>0.37 ± 0.25</t>
         </is>
       </c>
     </row>
@@ -936,42 +936,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gastropoda</t>
+          <t>Sphaeriidae</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.05</v>
+        <v>3.87</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>64.7</v>
+        <v>48.38</v>
       </c>
       <c r="F12" t="n">
         <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>0.74</v>
+        <v>1.88</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.4803</t>
+          <t>0.1640</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.80 ± 0.35</t>
+          <t>0.61 ± 0.21</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.37 ± 0.25</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.40 ± 0.21</t>
+          <t>0.87 ± 0.32</t>
         </is>
       </c>
     </row>
@@ -981,42 +981,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Gastropoda</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.51</v>
+        <v>4.45</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>16.04</v>
+        <v>62.3</v>
       </c>
       <c r="F13" t="n">
         <v>47</v>
       </c>
       <c r="G13" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.4821</t>
+          <t>0.1975</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.27 ± 0.12</t>
+          <t>0.57 ± 0.23</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.39 ± 0.25</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.13 ± 0.07</t>
+          <t>0.96 ± 0.39</t>
         </is>
       </c>
     </row>
@@ -1026,42 +1026,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hirudinea</t>
+          <t>Hydropsychidae</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.13</v>
+        <v>0.73</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>4.96</v>
+        <v>12.48</v>
       </c>
       <c r="F14" t="n">
         <v>47</v>
       </c>
       <c r="G14" t="n">
-        <v>0.63</v>
+        <v>1.37</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.5373</t>
+          <t>0.2651</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>0.19 ± 0.09</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.47 ± 0.23</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>0.10 ± 0.10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.13 ± 0.07</t>
         </is>
       </c>
     </row>
@@ -1071,42 +1071,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Caenis</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.18</v>
+        <v>2.79</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>7.47</v>
+        <v>56.01</v>
       </c>
       <c r="F15" t="n">
         <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.5759</t>
+          <t>0.3187</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.02 ± 0.02</t>
+          <t>0.62 ± 0.24</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.15 ± 0.15</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.14 ± 0.11</t>
+          <t>0.35 ± 0.21</t>
         </is>
       </c>
     </row>
@@ -1116,42 +1116,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hexagenia</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.2</v>
+        <v>0.27</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>50.5</v>
+        <v>7.38</v>
       </c>
       <c r="F16" t="n">
         <v>47</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.5745</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.34 ± 0.18</t>
+          <t>0.08 ± 0.07</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.31 ± 0.22</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.65 ± 0.32</t>
+          <t>0.23 ± 0.19</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hydropsychidae</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>12.98</v>
+        <v>16.24</v>
       </c>
       <c r="F17" t="n">
         <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.6584</t>
+          <t>0.6464</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.15 ± 0.11</t>
+          <t>0.24 ± 0.08</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.32 ± 0.17</t>
+          <t>0.40 ± 0.33</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.22 ± 0.12</t>
+          <t>0.14 ± 0.14</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1231,13 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J19" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K19" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
